--- a/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0002T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T6020_W0056F0002T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.42220510185596</v>
+        <v>2.343608329051593</v>
       </c>
       <c r="D2" t="n">
-        <v>34.67129935265086</v>
+        <v>5.634086144805765</v>
       </c>
       <c r="E2" t="n">
-        <v>15.9568696476791</v>
+        <v>2.592991317747854</v>
       </c>
       <c r="F2" t="n">
-        <v>7.915944105966961</v>
+        <v>1.286340917219631</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.79908615905196</v>
+        <v>2.892351500845943</v>
       </c>
       <c r="D3" t="n">
-        <v>18.68819416902319</v>
+        <v>3.036831552466269</v>
       </c>
       <c r="E3" t="n">
-        <v>15.9568696476791</v>
+        <v>2.592991317747854</v>
       </c>
       <c r="F3" t="n">
-        <v>7.915944105966961</v>
+        <v>1.286340917219631</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.61208357514626</v>
+        <v>8.549463580961268</v>
       </c>
       <c r="D4" t="n">
-        <v>33.45023788310075</v>
+        <v>5.435663656003872</v>
       </c>
       <c r="E4" t="n">
-        <v>15.9568696476791</v>
+        <v>2.592991317747854</v>
       </c>
       <c r="F4" t="n">
-        <v>7.915944105966961</v>
+        <v>1.286340917219631</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.60420440587264</v>
+        <v>6.760683215954304</v>
       </c>
       <c r="D5" t="n">
-        <v>42.55042660211964</v>
+        <v>6.914444322844442</v>
       </c>
       <c r="E5" t="n">
-        <v>15.9568696476791</v>
+        <v>2.592991317747854</v>
       </c>
       <c r="F5" t="n">
-        <v>7.915944105966961</v>
+        <v>1.286340917219631</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>49.14418791745837</v>
+        <v>7.985930536586985</v>
       </c>
       <c r="D6" t="n">
-        <v>36.81478206100839</v>
+        <v>5.982402084913864</v>
       </c>
       <c r="E6" t="n">
-        <v>15.9568696476791</v>
+        <v>2.592991317747854</v>
       </c>
       <c r="F6" t="n">
-        <v>7.915944105966961</v>
+        <v>1.286340917219631</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
